--- a/results/BRCA_Results_2025_V6.xlsx
+++ b/results/BRCA_Results_2025_V6.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="23">
   <si>
     <t>Metric</t>
   </si>
@@ -2925,7 +2925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2944,7 +2944,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>13196</v>
+        <v>13210</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2952,7 +2952,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>2878</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2960,7 +2960,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2968,7 +2968,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>2701</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>13961</v>
+        <v>13992</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2990,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>2081</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3001,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>3025</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3012,7 +3012,7 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>651</v>
+        <v>660</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3023,7 +3023,7 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3034,7 +3034,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3045,7 +3045,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3056,7 +3056,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3067,7 +3067,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3122,7 +3122,7 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3133,7 +3133,7 @@
         <v>14</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3163,10 +3163,10 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3174,7 +3174,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -3185,10 +3185,10 @@
         <v>22</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3196,10 +3196,10 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3207,10 +3207,10 @@
         <v>22</v>
       </c>
       <c r="B27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -3218,10 +3218,10 @@
         <v>22</v>
       </c>
       <c r="B28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3229,7 +3229,7 @@
         <v>22</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -3240,7 +3240,7 @@
         <v>22</v>
       </c>
       <c r="B30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -3251,7 +3251,7 @@
         <v>22</v>
       </c>
       <c r="B31">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -3259,13 +3259,13 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C32">
-        <v>208</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3273,10 +3273,10 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>42</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -3284,10 +3284,10 @@
         <v>8</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3295,10 +3295,10 @@
         <v>8</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -3306,10 +3306,10 @@
         <v>8</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -3317,10 +3317,10 @@
         <v>8</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -3328,10 +3328,10 @@
         <v>8</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3339,10 +3339,10 @@
         <v>8</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -3350,10 +3350,10 @@
         <v>8</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -3361,7 +3361,7 @@
         <v>8</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -3372,10 +3372,10 @@
         <v>8</v>
       </c>
       <c r="B42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3383,10 +3383,10 @@
         <v>8</v>
       </c>
       <c r="B43">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -3394,10 +3394,10 @@
         <v>8</v>
       </c>
       <c r="B44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -3405,10 +3405,10 @@
         <v>8</v>
       </c>
       <c r="B45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -3416,7 +3416,7 @@
         <v>8</v>
       </c>
       <c r="B46">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -3427,10 +3427,10 @@
         <v>8</v>
       </c>
       <c r="B47">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -3438,10 +3438,10 @@
         <v>8</v>
       </c>
       <c r="B48">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -3449,10 +3449,10 @@
         <v>8</v>
       </c>
       <c r="B49">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -3460,10 +3460,10 @@
         <v>8</v>
       </c>
       <c r="B50">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -3471,10 +3471,10 @@
         <v>8</v>
       </c>
       <c r="B51">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -3482,10 +3482,10 @@
         <v>8</v>
       </c>
       <c r="B52">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -3493,7 +3493,7 @@
         <v>8</v>
       </c>
       <c r="B53">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -3501,35 +3501,35 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C54">
-        <v>13753</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C55">
-        <v>2039</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C56">
-        <v>3009</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -3537,10 +3537,10 @@
         <v>9</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>616</v>
+        <v>13783</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -3548,10 +3548,10 @@
         <v>9</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>149</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -3559,10 +3559,10 @@
         <v>9</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>41</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -3570,10 +3570,10 @@
         <v>9</v>
       </c>
       <c r="B60">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>31</v>
+        <v>625</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -3581,10 +3581,10 @@
         <v>9</v>
       </c>
       <c r="B61">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C61">
-        <v>76</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -3592,10 +3592,10 @@
         <v>9</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C62">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -3603,10 +3603,10 @@
         <v>9</v>
       </c>
       <c r="B63">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -3614,10 +3614,10 @@
         <v>9</v>
       </c>
       <c r="B64">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -3625,10 +3625,10 @@
         <v>9</v>
       </c>
       <c r="B65">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -3636,10 +3636,10 @@
         <v>9</v>
       </c>
       <c r="B66">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -3647,10 +3647,10 @@
         <v>9</v>
       </c>
       <c r="B67">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -3658,10 +3658,10 @@
         <v>9</v>
       </c>
       <c r="B68">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -3669,10 +3669,10 @@
         <v>9</v>
       </c>
       <c r="B69">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -3680,7 +3680,7 @@
         <v>9</v>
       </c>
       <c r="B70">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -3691,10 +3691,10 @@
         <v>9</v>
       </c>
       <c r="B71">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -3702,7 +3702,7 @@
         <v>9</v>
       </c>
       <c r="B72">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -3713,10 +3713,10 @@
         <v>9</v>
       </c>
       <c r="B73">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -3724,7 +3724,7 @@
         <v>9</v>
       </c>
       <c r="B74">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -3735,7 +3735,7 @@
         <v>9</v>
       </c>
       <c r="B75">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3746,7 +3746,7 @@
         <v>9</v>
       </c>
       <c r="B76">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -3754,32 +3754,32 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C77">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C78">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -3790,10 +3790,10 @@
         <v>10</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -3801,10 +3801,10 @@
         <v>10</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -3812,10 +3812,10 @@
         <v>10</v>
       </c>
       <c r="B82">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -3823,10 +3823,10 @@
         <v>10</v>
       </c>
       <c r="B83">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -3834,10 +3834,10 @@
         <v>10</v>
       </c>
       <c r="B84">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -3845,10 +3845,10 @@
         <v>10</v>
       </c>
       <c r="B85">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -3856,10 +3856,10 @@
         <v>10</v>
       </c>
       <c r="B86">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C86">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -3867,7 +3867,7 @@
         <v>10</v>
       </c>
       <c r="B87">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -3878,10 +3878,10 @@
         <v>10</v>
       </c>
       <c r="B88">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -3889,10 +3889,10 @@
         <v>10</v>
       </c>
       <c r="B89">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -3900,7 +3900,7 @@
         <v>10</v>
       </c>
       <c r="B90">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -3911,10 +3911,10 @@
         <v>10</v>
       </c>
       <c r="B91">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -3922,10 +3922,10 @@
         <v>10</v>
       </c>
       <c r="B92">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -3933,10 +3933,10 @@
         <v>10</v>
       </c>
       <c r="B93">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -3944,7 +3944,7 @@
         <v>10</v>
       </c>
       <c r="B94">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -3955,7 +3955,7 @@
         <v>10</v>
       </c>
       <c r="B95">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -3966,7 +3966,7 @@
         <v>10</v>
       </c>
       <c r="B96">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -3977,7 +3977,7 @@
         <v>10</v>
       </c>
       <c r="B97">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -3988,10 +3988,10 @@
         <v>10</v>
       </c>
       <c r="B98">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -3999,7 +3999,7 @@
         <v>10</v>
       </c>
       <c r="B99">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -4010,10 +4010,10 @@
         <v>10</v>
       </c>
       <c r="B100">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -4021,10 +4021,10 @@
         <v>10</v>
       </c>
       <c r="B101">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -4032,10 +4032,10 @@
         <v>10</v>
       </c>
       <c r="B102">
-        <v>237</v>
+        <v>102</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -4043,7 +4043,7 @@
         <v>10</v>
       </c>
       <c r="B103">
-        <v>258</v>
+        <v>132</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -4054,7 +4054,7 @@
         <v>10</v>
       </c>
       <c r="B104">
-        <v>462</v>
+        <v>179</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4065,10 +4065,10 @@
         <v>10</v>
       </c>
       <c r="B105">
-        <v>1706</v>
+        <v>237</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -4076,7 +4076,7 @@
         <v>10</v>
       </c>
       <c r="B106">
-        <v>4063</v>
+        <v>258</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4087,7 +4087,7 @@
         <v>10</v>
       </c>
       <c r="B107">
-        <v>4092</v>
+        <v>462</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -4095,35 +4095,35 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>1706</v>
       </c>
       <c r="C108">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>4074</v>
       </c>
       <c r="C109">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>4095</v>
       </c>
       <c r="C110">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -4131,10 +4131,10 @@
         <v>11</v>
       </c>
       <c r="B111">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -4142,10 +4142,10 @@
         <v>11</v>
       </c>
       <c r="B112">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -4153,10 +4153,10 @@
         <v>11</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -4164,10 +4164,10 @@
         <v>11</v>
       </c>
       <c r="B114">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -4175,7 +4175,7 @@
         <v>11</v>
       </c>
       <c r="B115">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -4186,10 +4186,10 @@
         <v>11</v>
       </c>
       <c r="B116">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -4197,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="B117">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -4208,10 +4208,10 @@
         <v>11</v>
       </c>
       <c r="B118">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C118">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -4219,10 +4219,10 @@
         <v>11</v>
       </c>
       <c r="B119">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -4230,10 +4230,10 @@
         <v>11</v>
       </c>
       <c r="B120">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -4241,10 +4241,10 @@
         <v>11</v>
       </c>
       <c r="B121">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -4252,10 +4252,10 @@
         <v>11</v>
       </c>
       <c r="B122">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -4263,43 +4263,43 @@
         <v>11</v>
       </c>
       <c r="B123">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C124">
-        <v>77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C125">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="C126">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -4307,10 +4307,10 @@
         <v>12</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -4318,10 +4318,10 @@
         <v>12</v>
       </c>
       <c r="B128">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -4329,10 +4329,10 @@
         <v>12</v>
       </c>
       <c r="B129">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -4340,10 +4340,10 @@
         <v>12</v>
       </c>
       <c r="B130">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -4351,10 +4351,10 @@
         <v>12</v>
       </c>
       <c r="B131">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C131">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -4362,10 +4362,10 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -4373,10 +4373,10 @@
         <v>12</v>
       </c>
       <c r="B133">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -4384,32 +4384,32 @@
         <v>12</v>
       </c>
       <c r="B134">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C135">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C136">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -4417,10 +4417,10 @@
         <v>13</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -4428,10 +4428,10 @@
         <v>13</v>
       </c>
       <c r="B138">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -4439,10 +4439,10 @@
         <v>13</v>
       </c>
       <c r="B139">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -4450,10 +4450,10 @@
         <v>13</v>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C140">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -4461,7 +4461,7 @@
         <v>13</v>
       </c>
       <c r="B141">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C141">
         <v>11</v>
@@ -4472,7 +4472,7 @@
         <v>13</v>
       </c>
       <c r="B142">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C142">
         <v>11</v>
@@ -4483,10 +4483,10 @@
         <v>13</v>
       </c>
       <c r="B143">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C143">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -4494,32 +4494,32 @@
         <v>13</v>
       </c>
       <c r="B144">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C144">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C145">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C146">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -4527,10 +4527,10 @@
         <v>14</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -4538,10 +4538,10 @@
         <v>14</v>
       </c>
       <c r="B148">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -4549,10 +4549,10 @@
         <v>14</v>
       </c>
       <c r="B149">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C149">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -4560,10 +4560,10 @@
         <v>14</v>
       </c>
       <c r="B150">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C150">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -4571,7 +4571,7 @@
         <v>14</v>
       </c>
       <c r="B151">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C151">
         <v>11</v>
@@ -4582,7 +4582,7 @@
         <v>14</v>
       </c>
       <c r="B152">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C152">
         <v>11</v>
@@ -4593,10 +4593,10 @@
         <v>14</v>
       </c>
       <c r="B153">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C153">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -4604,32 +4604,32 @@
         <v>14</v>
       </c>
       <c r="B154">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C154">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B155">
+        <v>9</v>
       </c>
       <c r="C155">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="B156">
+        <v>10</v>
       </c>
       <c r="C156">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -4637,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C157">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -4648,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C158">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C159">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -4670,9 +4670,31 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
+        <v>19</v>
+      </c>
+      <c r="C160">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
         <v>21</v>
       </c>
-      <c r="C160">
+      <c r="C162">
         <v>20</v>
       </c>
     </row>
